--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_16-10-2025.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
